--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135855881</v>
       </c>
       <c r="B19" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135856003</v>
       </c>
       <c r="B20" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135856111</v>
       </c>
       <c r="B21" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135854718</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135855464</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135855490</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>135856208</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>135856260</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135856307</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135856422</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135856453</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135856484</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135856505</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135855881</v>
       </c>
       <c r="B19" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135856003</v>
       </c>
       <c r="B20" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135856111</v>
       </c>
       <c r="B21" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135854718</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135855464</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135855490</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>135856208</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>135856260</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135856307</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135856422</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135856453</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135856484</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135856505</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135855881</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135856003</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135856111</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135854718</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135855464</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135855490</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>135856208</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>135856260</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135856307</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135856422</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135856453</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135856484</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135856505</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135855881</v>
       </c>
       <c r="B19" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135856003</v>
       </c>
       <c r="B20" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135856111</v>
       </c>
       <c r="B21" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135854718</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135855464</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135855490</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>135856208</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>135856260</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135856307</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135856422</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135856453</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135856484</v>
       </c>
       <c r="B30" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135856505</v>
       </c>
       <c r="B31" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92305</v>
+        <v>92312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135855881</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135856003</v>
       </c>
       <c r="B20" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135856111</v>
       </c>
       <c r="B21" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135854718</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135855464</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135855490</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>135856208</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>135856260</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135856307</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135856422</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135856453</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135856484</v>
       </c>
       <c r="B30" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135856505</v>
       </c>
       <c r="B31" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92313</v>
+        <v>92326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135855881</v>
       </c>
       <c r="B19" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135856003</v>
       </c>
       <c r="B20" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135856111</v>
       </c>
       <c r="B21" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135854718</v>
       </c>
       <c r="B22" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135855464</v>
       </c>
       <c r="B23" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135855490</v>
       </c>
       <c r="B24" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>135856208</v>
       </c>
       <c r="B25" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>135856260</v>
       </c>
       <c r="B26" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135856307</v>
       </c>
       <c r="B27" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135856422</v>
       </c>
       <c r="B28" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135856453</v>
       </c>
       <c r="B29" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135856484</v>
       </c>
       <c r="B30" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135856505</v>
       </c>
       <c r="B31" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 62084-2022 artfynd.xlsx
+++ b/artfynd/A 62084-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855387</v>
       </c>
       <c r="B2" t="n">
-        <v>92721</v>
+        <v>92722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135855298</v>
       </c>
       <c r="B3" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>135855587</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135855938</v>
       </c>
       <c r="B5" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135858109</v>
       </c>
       <c r="B6" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135854651</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>135855069</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135855622</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135855767</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135856081</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135856029</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>135855062</v>
       </c>
       <c r="B13" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135855590</v>
       </c>
       <c r="B14" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135854659</v>
       </c>
       <c r="B15" t="n">
-        <v>92326</v>
+        <v>92327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>135855631</v>
       </c>
       <c r="B16" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135858146</v>
       </c>
       <c r="B17" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135854584</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>135856135</v>
       </c>
       <c r="B32" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135855216</v>
       </c>
       <c r="B33" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>135855780</v>
       </c>
       <c r="B34" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
